--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 59 D100 Spring 2024 24GE03I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 59 D100 Spring 2024 24GE03I13 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gl Lab User\Desktop\GLNPO Spring\GLNPO Spring 2024\Erie\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983440CF-20B6-4D56-A43F-5AFCEABD205E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C3FE0A-854D-423B-B4F5-1C1530D1D46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{11156D9B-5AB0-4437-A25B-9CFD157AFBBF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{11156D9B-5AB0-4437-A25B-9CFD157AFBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6541" r:id="rId2"/>
+    <pivotCache cacheId="5" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5877,7 +5877,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2050200-060D-460B-9BC9-1DAB88050602}" name="PivotTable1" cacheId="6541" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2050200-060D-460B-9BC9-1DAB88050602}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:X25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6352,16 +6352,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD089B7-B1C0-4526-A3DF-06A7654C0D5B}">
   <dimension ref="A1:X268"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6417,7 +6418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6476,7 +6477,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6544,7 +6545,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>35</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O4">
         <v>1.341</v>
@@ -6612,7 +6613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6677,7 +6678,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6813,7 +6814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6881,7 +6882,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6946,7 +6947,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -7082,7 +7083,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -7150,7 +7151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -7191,7 +7192,7 @@
         <v>35</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O13">
         <v>1.163</v>
@@ -7218,7 +7219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7286,7 +7287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7351,7 +7352,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7481,7 +7482,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7549,7 +7550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7685,7 +7686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7726,7 +7727,7 @@
         <v>35</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O21">
         <v>1.526</v>
@@ -7753,7 +7754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7821,7 +7822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7957,7 +7958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -8025,7 +8026,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -8078,7 +8079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -8193,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -8234,7 +8235,7 @@
         <v>35</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O29">
         <v>1.4179999999999999</v>
@@ -8253,7 +8254,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -8315,7 +8316,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8375,7 +8376,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -8434,7 +8435,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -8493,7 +8494,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8534,7 +8535,7 @@
         <v>35</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O34">
         <v>1.6160000000000001</v>
@@ -8550,7 +8551,7 @@
       </c>
       <c r="U34" s="8"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8603,7 +8604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8656,7 +8657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8709,7 +8710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8750,7 +8751,7 @@
         <v>35</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O38">
         <v>1.2150000000000001</v>
@@ -8762,7 +8763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8815,7 +8816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8856,7 +8857,7 @@
         <v>35</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O40">
         <v>1.159</v>
@@ -8868,7 +8869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8921,7 +8922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9016,7 @@
         <v>35</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O43">
         <v>1.347</v>
@@ -9027,7 +9028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -9080,7 +9081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9133,7 +9134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -9186,7 +9187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -9239,7 +9240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -9280,7 +9281,7 @@
         <v>35</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O48">
         <v>1.4530000000000001</v>
@@ -9292,7 +9293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -9345,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -9398,7 +9399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9492,7 +9493,7 @@
         <v>35</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O52">
         <v>1.44</v>
@@ -9504,7 +9505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9610,7 +9611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9663,7 +9664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9704,7 +9705,7 @@
         <v>35</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O56">
         <v>1.5669999999999999</v>
@@ -9716,7 +9717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9757,7 +9758,7 @@
         <v>35</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O57">
         <v>1.4870000000000001</v>
@@ -9769,7 +9770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9822,7 +9823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9875,7 +9876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9981,7 +9982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -10087,7 +10088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -10140,7 +10141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -10193,7 +10194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10235,7 @@
         <v>35</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O66">
         <v>1.216</v>
@@ -10246,7 +10247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>35</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O67">
         <v>1.3819999999999999</v>
@@ -10299,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10341,7 @@
         <v>35</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O68">
         <v>1.4790000000000001</v>
@@ -10352,7 +10353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -10405,7 +10406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -10458,7 +10459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10511,7 +10512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10564,7 +10565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10670,7 +10671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10723,7 +10724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10776,7 +10777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10829,7 +10830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10871,7 @@
         <v>35</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O78">
         <v>1.296</v>
@@ -10882,7 +10883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10935,7 +10936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10988,7 +10989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -11041,7 +11042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -11094,7 +11095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -11135,7 +11136,7 @@
         <v>35</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O83">
         <v>1.282</v>
@@ -11147,7 +11148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -11188,7 +11189,7 @@
         <v>35</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O84">
         <v>1.4830000000000001</v>
@@ -11200,7 +11201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -11253,7 +11254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -11306,7 +11307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -11359,7 +11360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -11400,7 +11401,7 @@
         <v>35</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O88">
         <v>1.331</v>
@@ -11412,7 +11413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -11465,7 +11466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11518,7 +11519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11559,7 +11560,7 @@
         <v>35</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O91">
         <v>1.3240000000000001</v>
@@ -11571,7 +11572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11624,7 +11625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11677,7 +11678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11730,7 +11731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11783,7 +11784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11836,7 +11837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11889,7 +11890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11942,7 +11943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11995,7 +11996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -12048,7 +12049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -12101,7 +12102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -12154,7 +12155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -12207,7 +12208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -12260,7 +12261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -12313,7 +12314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -12366,7 +12367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -12419,7 +12420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -12472,7 +12473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12525,7 +12526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12578,7 +12579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12631,7 +12632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12684,7 +12685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12737,7 +12738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12790,7 +12791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12843,7 +12844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12896,7 +12897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12949,7 +12950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -13002,7 +13003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -13055,7 +13056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -13108,7 +13109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -13161,7 +13162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -13214,7 +13215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -13267,7 +13268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -13320,7 +13321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -13373,7 +13374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -13426,7 +13427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13479,7 +13480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13532,7 +13533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13585,7 +13586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13638,7 +13639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13691,7 +13692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13744,7 +13745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13797,7 +13798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13853,7 +13854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13906,7 +13907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13946,8 +13947,8 @@
       <c r="M136" t="s">
         <v>70</v>
       </c>
-      <c r="N136" t="s">
-        <v>70</v>
+      <c r="N136" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O136">
         <v>1.32</v>
@@ -13959,7 +13960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -14012,7 +14013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -14065,7 +14066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -14118,7 +14119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -14171,7 +14172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -14224,7 +14225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -14277,7 +14278,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -14330,7 +14331,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -14371,7 +14372,7 @@
         <v>35</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O144" t="s">
         <v>29</v>
@@ -14383,7 +14384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -14424,7 +14425,7 @@
         <v>35</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O145" t="s">
         <v>29</v>
@@ -14436,7 +14437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14489,7 +14490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14542,7 +14543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14595,7 +14596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14648,7 +14649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14701,7 +14702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14754,7 +14755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14807,7 +14808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14860,7 +14861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14913,7 +14914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14966,7 +14967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -15019,7 +15020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -15072,7 +15073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -15125,7 +15126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -15178,7 +15179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -15231,7 +15232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -15284,7 +15285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -15337,7 +15338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -15390,7 +15391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -15443,7 +15444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15496,7 +15497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15549,7 +15550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15602,7 +15603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15655,7 +15656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15708,7 +15709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15761,7 +15762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15814,7 +15815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15867,7 +15868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15920,7 +15921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15973,7 +15974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -16026,7 +16027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -16079,7 +16080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -16132,7 +16133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -16185,7 +16186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -16238,7 +16239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -16291,7 +16292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -16344,7 +16345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -16397,7 +16398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -16450,7 +16451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16503,7 +16504,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16556,7 +16557,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16597,7 +16598,7 @@
         <v>35</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O186" t="s">
         <v>29</v>
@@ -16609,7 +16610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16650,7 +16651,7 @@
         <v>35</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O187" t="s">
         <v>29</v>
@@ -16662,7 +16663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16715,7 +16716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16768,7 +16769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16821,7 +16822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16861,8 +16862,8 @@
       <c r="M191" t="s">
         <v>70</v>
       </c>
-      <c r="N191" t="s">
-        <v>70</v>
+      <c r="N191" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O191">
         <v>0.65200000000000002</v>
@@ -16877,7 +16878,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16930,7 +16931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16983,7 +16984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -17036,7 +17037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -17089,7 +17090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -17142,7 +17143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -17195,7 +17196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -17248,7 +17249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -17301,7 +17302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -17354,7 +17355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -17407,7 +17408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17460,7 +17461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17513,7 +17514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17566,7 +17567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17619,7 +17620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17672,7 +17673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17725,7 +17726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17778,7 +17779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17818,8 +17819,8 @@
       <c r="M209" t="s">
         <v>70</v>
       </c>
-      <c r="N209" t="s">
-        <v>70</v>
+      <c r="N209" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O209">
         <v>0.51900000000000002</v>
@@ -17831,7 +17832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17884,7 +17885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17937,7 +17938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17990,7 +17991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -18043,7 +18044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -18096,7 +18097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -18149,7 +18150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -18202,7 +18203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -18255,7 +18256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -18308,7 +18309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -18361,7 +18362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -18414,7 +18415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18467,7 +18468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18520,7 +18521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18573,7 +18574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18626,7 +18627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18679,7 +18680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18732,7 +18733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18785,7 +18786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18838,7 +18839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18891,7 +18892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -18944,7 +18945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18997,7 +18998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -19050,7 +19051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -19103,7 +19104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -19156,7 +19157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -19209,7 +19210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -19262,7 +19263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -19315,7 +19316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -19368,7 +19369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -19421,7 +19422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -19474,7 +19475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -19527,7 +19528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -19580,7 +19581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -19633,7 +19634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -19686,7 +19687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -19739,7 +19740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -19792,7 +19793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -19845,7 +19846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -19898,7 +19899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -19951,7 +19952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -20004,7 +20005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -20057,7 +20058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -20110,7 +20111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -20163,7 +20164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>18</v>
       </c>
@@ -20216,7 +20217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>18</v>
       </c>
@@ -20269,7 +20270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>18</v>
       </c>
@@ -20322,7 +20323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>18</v>
       </c>
@@ -20375,7 +20376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>18</v>
       </c>
@@ -20428,7 +20429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>18</v>
       </c>
@@ -20468,8 +20469,8 @@
       <c r="M259" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N259" s="4" t="s">
-        <v>70</v>
+      <c r="N259" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O259" s="4" t="s">
         <v>29</v>
@@ -20481,7 +20482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>18</v>
       </c>
@@ -20521,8 +20522,8 @@
       <c r="M260" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N260" s="4" t="s">
-        <v>70</v>
+      <c r="N260" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O260" s="4" t="s">
         <v>29</v>
@@ -20534,7 +20535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>18</v>
       </c>
@@ -20587,7 +20588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>18</v>
       </c>
@@ -20640,7 +20641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>18</v>
       </c>
@@ -20693,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>18</v>
       </c>
@@ -20746,7 +20747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>18</v>
       </c>
@@ -20786,8 +20787,8 @@
       <c r="M265" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N265" s="4" t="s">
-        <v>70</v>
+      <c r="N265" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O265" s="4" t="s">
         <v>29</v>
@@ -20799,7 +20800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>18</v>
       </c>
@@ -20839,8 +20840,8 @@
       <c r="M266" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N266" s="4" t="s">
-        <v>70</v>
+      <c r="N266" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="O266" s="4" t="s">
         <v>29</v>
@@ -20852,7 +20853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>18</v>
       </c>
@@ -20905,7 +20906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>18</v>
       </c>
@@ -20959,7 +20960,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R268" xr:uid="{1AD089B7-B1C0-4526-A3DF-06A7654C0D5B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>